--- a/data/satisfaction_detail/2026/6月/酒店餐饮客户.xlsx
+++ b/data/satisfaction_detail/2026/6月/酒店餐饮客户.xlsx
@@ -475,7 +475,7 @@
         <v>9.82</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="3">
@@ -488,7 +488,7 @@
         <v>9.880000000000001</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="4">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>9.94</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>10</v>
@@ -576,10 +576,10 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>9.75</v>
+        <v>9.77</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>9.949999999999999</v>
+        <v>9.960000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -615,10 +615,10 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>9.609999999999999</v>
+        <v>9.57</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>10</v>
+        <v>9.960000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -655,10 +655,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>9.76</v>
+        <v>9.75</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="18">
@@ -668,10 +668,10 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>9.609999999999999</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="19">
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>9.84</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>10</v>
+        <v>9.960000000000001</v>
       </c>
     </row>
     <row r="22">
